--- a/public/templates/template_kelas.xlsx
+++ b/public/templates/template_kelas.xlsx
@@ -427,7 +427,6 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
